--- a/timetable_generator/timetable_outputs/CSE_Sem5_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/CSE_Sem5_SectionA_Timetable.xlsx
@@ -468,30 +468,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CS309
+Statistics for computer science
+C101
+Dr. Sunil C K
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CS309
+Statistics for computer science
+C101
+Dr. Sunil C K</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CS304
 Artificial intelligence
 C101
 Dr. krishnendu</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CS309
-Statistics for computer science
-C101
-Dr. Sunil C K</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CS304
-Artificial intelligence
-C101
-Dr. krishnendu</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,38 +501,18 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CS303
-Computer networks 
-C101
-Dr. Animesh Roy</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>CS309
-Statistics for computer science
-C101
-Dr. Sunil C K</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CS303
-Computer networks 
-C101
-Dr. Animesh Roy</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>CS304
 Artificial intelligence
 C101
-Dr. krishnendu</t>
-        </is>
-      </c>
+Dr. krishnendu
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,7 +520,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CS309
+Statistics for computer science
+C101
+Dr. Sunil C K</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -551,7 +539,15 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CS303
+Computer networks 
+C101
+Dr. Animesh Roy
+[TUTORIAL]</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
@@ -561,15 +557,15 @@
 Dr. Animesh Roy</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CS309
-Statistics for computer science
-C101
-Dr. Sunil C K</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CS303
+Computer networks 
+C101
+Dr. Animesh Roy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -579,13 +575,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>CS304
+Artificial intelligence
+C101
+Dr. krishnendu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>CS303
 Computer networks 
 C101
 Dr. Animesh Roy</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
